--- a/regression_deneme/regression_with_nn/konak_weekly_true_and_predicted_test.xlsx
+++ b/regression_deneme/regression_with_nn/konak_weekly_true_and_predicted_test.xlsx
@@ -461,7 +461,7 @@
         <v>18</v>
       </c>
       <c r="D2" t="n">
-        <v>10.18089400140914</v>
+        <v>10.69661330788151</v>
       </c>
     </row>
     <row r="3">
@@ -475,7 +475,7 @@
         <v>60</v>
       </c>
       <c r="D3" t="n">
-        <v>48.91696644141096</v>
+        <v>53.78056276794291</v>
       </c>
     </row>
     <row r="4">
@@ -489,7 +489,7 @@
         <v>76</v>
       </c>
       <c r="D4" t="n">
-        <v>55.54385897909442</v>
+        <v>60.9433506975444</v>
       </c>
     </row>
     <row r="5">
@@ -503,7 +503,7 @@
         <v>59</v>
       </c>
       <c r="D5" t="n">
-        <v>58.81426579863967</v>
+        <v>69.20936523543344</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         <v>31</v>
       </c>
       <c r="D6" t="n">
-        <v>51.50495885227271</v>
+        <v>61.50614315463409</v>
       </c>
     </row>
     <row r="7">
@@ -531,7 +531,7 @@
         <v>36</v>
       </c>
       <c r="D7" t="n">
-        <v>49.76840847623059</v>
+        <v>50.46793578400614</v>
       </c>
     </row>
     <row r="8">
@@ -545,7 +545,7 @@
         <v>63</v>
       </c>
       <c r="D8" t="n">
-        <v>44.53493604664891</v>
+        <v>44.55166605702702</v>
       </c>
     </row>
     <row r="9">
@@ -559,7 +559,7 @@
         <v>37</v>
       </c>
       <c r="D9" t="n">
-        <v>44.94454193558638</v>
+        <v>49.71050936792113</v>
       </c>
     </row>
     <row r="10">
@@ -573,7 +573,7 @@
         <v>49</v>
       </c>
       <c r="D10" t="n">
-        <v>46.90808190511951</v>
+        <v>51.40759934310834</v>
       </c>
     </row>
     <row r="11">
@@ -587,7 +587,7 @@
         <v>27</v>
       </c>
       <c r="D11" t="n">
-        <v>41.68558809583566</v>
+        <v>37.83196639595243</v>
       </c>
     </row>
     <row r="12">
@@ -601,7 +601,7 @@
         <v>40</v>
       </c>
       <c r="D12" t="n">
-        <v>38.55020619863065</v>
+        <v>44.88387165648605</v>
       </c>
     </row>
     <row r="13">
@@ -615,7 +615,7 @@
         <v>39</v>
       </c>
       <c r="D13" t="n">
-        <v>37.25825624672181</v>
+        <v>42.79968074474878</v>
       </c>
     </row>
     <row r="14">
@@ -629,7 +629,7 @@
         <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>42.12135460040728</v>
+        <v>46.19336353931336</v>
       </c>
     </row>
     <row r="15">
@@ -643,7 +643,7 @@
         <v>32</v>
       </c>
       <c r="D15" t="n">
-        <v>39.74680869177752</v>
+        <v>42.89742271561313</v>
       </c>
     </row>
     <row r="16">
@@ -657,7 +657,7 @@
         <v>46</v>
       </c>
       <c r="D16" t="n">
-        <v>40.13633466173522</v>
+        <v>48.64410581267867</v>
       </c>
     </row>
     <row r="17">
@@ -671,7 +671,7 @@
         <v>44</v>
       </c>
       <c r="D17" t="n">
-        <v>35.67886560390036</v>
+        <v>43.70403277293261</v>
       </c>
     </row>
     <row r="18">
@@ -685,7 +685,7 @@
         <v>48</v>
       </c>
       <c r="D18" t="n">
-        <v>43.0935684846524</v>
+        <v>46.69074247933412</v>
       </c>
     </row>
     <row r="19">
@@ -699,7 +699,7 @@
         <v>27</v>
       </c>
       <c r="D19" t="n">
-        <v>41.30635451364016</v>
+        <v>43.33679838448511</v>
       </c>
     </row>
     <row r="20">
@@ -713,7 +713,7 @@
         <v>17</v>
       </c>
       <c r="D20" t="n">
-        <v>30.22077078297329</v>
+        <v>33.90262326057993</v>
       </c>
     </row>
     <row r="21">
@@ -727,7 +727,7 @@
         <v>40</v>
       </c>
       <c r="D21" t="n">
-        <v>31.94914916504414</v>
+        <v>26.30241425118097</v>
       </c>
     </row>
     <row r="22">
@@ -741,7 +741,7 @@
         <v>43</v>
       </c>
       <c r="D22" t="n">
-        <v>36.07105812121826</v>
+        <v>36.80325052415144</v>
       </c>
     </row>
     <row r="23">
@@ -755,7 +755,7 @@
         <v>43</v>
       </c>
       <c r="D23" t="n">
-        <v>38.25553892780925</v>
+        <v>42.57452195902741</v>
       </c>
     </row>
     <row r="24">
@@ -769,7 +769,7 @@
         <v>46</v>
       </c>
       <c r="D24" t="n">
-        <v>44.40133481631086</v>
+        <v>48.82967920817497</v>
       </c>
     </row>
     <row r="25">
@@ -783,7 +783,7 @@
         <v>34</v>
       </c>
       <c r="D25" t="n">
-        <v>41.49465578791716</v>
+        <v>43.21618015455368</v>
       </c>
     </row>
     <row r="26">
@@ -797,7 +797,7 @@
         <v>46</v>
       </c>
       <c r="D26" t="n">
-        <v>44.0146877795701</v>
+        <v>46.84473734436661</v>
       </c>
     </row>
     <row r="27">
@@ -811,7 +811,7 @@
         <v>32</v>
       </c>
       <c r="D27" t="n">
-        <v>37.66640313510752</v>
+        <v>40.67523439820759</v>
       </c>
     </row>
     <row r="28">
@@ -825,7 +825,7 @@
         <v>39</v>
       </c>
       <c r="D28" t="n">
-        <v>40.18381849733568</v>
+        <v>43.91228633232075</v>
       </c>
     </row>
     <row r="29">
@@ -839,7 +839,7 @@
         <v>55</v>
       </c>
       <c r="D29" t="n">
-        <v>39.83975478051457</v>
+        <v>41.18593275788199</v>
       </c>
     </row>
     <row r="30">
@@ -853,7 +853,7 @@
         <v>37</v>
       </c>
       <c r="D30" t="n">
-        <v>41.80350610297717</v>
+        <v>46.8145701700686</v>
       </c>
     </row>
     <row r="31">
@@ -867,7 +867,7 @@
         <v>45</v>
       </c>
       <c r="D31" t="n">
-        <v>44.30330224467816</v>
+        <v>47.34189631773998</v>
       </c>
     </row>
     <row r="32">
@@ -881,7 +881,7 @@
         <v>41</v>
       </c>
       <c r="D32" t="n">
-        <v>40.84321451840435</v>
+        <v>42.22081536106366</v>
       </c>
     </row>
   </sheetData>
